--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1165,7 +1165,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827156</v>
+        <v>129827138</v>
       </c>
       <c r="B7" t="n">
         <v>91593</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574917</v>
+        <v>574868</v>
       </c>
       <c r="R7" t="n">
-        <v>7071640</v>
+        <v>7071732</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R8" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827138</v>
+        <v>129827192</v>
       </c>
       <c r="B9" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574868</v>
+        <v>574881</v>
       </c>
       <c r="R9" t="n">
-        <v>7071732</v>
+        <v>7071589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827187</v>
+        <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>92316</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575013</v>
+        <v>575031</v>
       </c>
       <c r="R10" t="n">
-        <v>7071709</v>
+        <v>7071787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1553,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827176</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>92316</v>
+        <v>91593</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575031</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071787</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,7 +1633,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827188</v>
+        <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>91593</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574912</v>
+        <v>574930</v>
       </c>
       <c r="R19" t="n">
-        <v>7071745</v>
+        <v>7071643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B20" t="n">
-        <v>91593</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R20" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,6 +2503,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2529,7 +2534,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827188</v>
       </c>
       <c r="B21" t="n">
         <v>80186</v>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574912</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>91593</v>
+        <v>92284</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R23" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>92284</v>
+        <v>91593</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R24" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B29" t="n">
-        <v>91891</v>
+        <v>91593</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827146</v>
+        <v>129827183</v>
       </c>
       <c r="B30" t="n">
-        <v>91593</v>
+        <v>91891</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574908</v>
+        <v>574913</v>
       </c>
       <c r="R30" t="n">
-        <v>7071600</v>
+        <v>7071700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B31" t="n">
-        <v>91593</v>
+        <v>88992</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R31" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827162</v>
+        <v>129827146</v>
       </c>
       <c r="B32" t="n">
-        <v>57736</v>
+        <v>91593</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574844</v>
+        <v>574908</v>
       </c>
       <c r="R32" t="n">
-        <v>7071940</v>
+        <v>7071600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3672,11 +3672,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3703,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>88992</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R33" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,10 +3800,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827164</v>
+        <v>129827196</v>
       </c>
       <c r="B34" t="n">
-        <v>57736</v>
+        <v>91613</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,23 +3811,19 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -3835,10 +3831,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574945</v>
+        <v>574833</v>
       </c>
       <c r="R34" t="n">
-        <v>7071651</v>
+        <v>7071729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3871,11 +3867,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3902,45 +3893,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827167</v>
+        <v>129835984</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>91806</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574886</v>
+        <v>574908</v>
       </c>
       <c r="R35" t="n">
-        <v>7071594</v>
+        <v>7071708</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3975,17 +3969,13 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4004,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827196</v>
+        <v>129827164</v>
       </c>
       <c r="B36" t="n">
-        <v>91613</v>
+        <v>57736</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4015,19 +4005,23 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4035,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574833</v>
+        <v>574945</v>
       </c>
       <c r="R36" t="n">
-        <v>7071729</v>
+        <v>7071651</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4071,6 +4065,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4097,48 +4096,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129835984</v>
+        <v>129827167</v>
       </c>
       <c r="B37" t="n">
-        <v>91806</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574908</v>
+        <v>574886</v>
       </c>
       <c r="R37" t="n">
-        <v>7071708</v>
+        <v>7071594</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4173,13 +4169,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827171</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92284</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574903</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071393</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,11 +4269,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B39" t="n">
-        <v>92284</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R39" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4397,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827185</v>
+        <v>129827171</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4408,21 +4403,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574754</v>
+        <v>574903</v>
       </c>
       <c r="R40" t="n">
-        <v>7071844</v>
+        <v>7071393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,6 +4463,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129827158</v>
       </c>
       <c r="B2" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91891</v>
+        <v>91895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129827138</v>
       </c>
       <c r="B7" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827156</v>
+        <v>129827192</v>
       </c>
       <c r="B8" t="n">
-        <v>91593</v>
+        <v>80186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574917</v>
+        <v>574881</v>
       </c>
       <c r="R8" t="n">
-        <v>7071640</v>
+        <v>7071589</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R9" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827187</v>
       </c>
       <c r="B10" t="n">
-        <v>92316</v>
+        <v>80186</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>575013</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,7 +1535,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B11" t="n">
-        <v>91593</v>
+        <v>92320</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1632,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>91597</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1848,7 +1848,7 @@
         <v>129827199</v>
       </c>
       <c r="B14" t="n">
-        <v>88992</v>
+        <v>88996</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827174</v>
+        <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574764</v>
+        <v>574912</v>
       </c>
       <c r="R20" t="n">
-        <v>7071692</v>
+        <v>7071745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,11 +2503,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2534,7 +2529,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827188</v>
+        <v>129827194</v>
       </c>
       <c r="B21" t="n">
         <v>80186</v>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574912</v>
+        <v>574878</v>
       </c>
       <c r="R21" t="n">
-        <v>7071745</v>
+        <v>7071591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2631,10 +2626,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827194</v>
+        <v>129827174</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2637,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574878</v>
+        <v>574764</v>
       </c>
       <c r="R22" t="n">
-        <v>7071591</v>
+        <v>7071692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2702,6 +2697,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2731,7 +2731,7 @@
         <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>92284</v>
+        <v>92288</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827141</v>
+        <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>91593</v>
+        <v>91895</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574904</v>
+        <v>574913</v>
       </c>
       <c r="R29" t="n">
-        <v>7071706</v>
+        <v>7071700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827183</v>
+        <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>91891</v>
+        <v>88996</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574913</v>
+        <v>574842</v>
       </c>
       <c r="R30" t="n">
-        <v>7071700</v>
+        <v>7071778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B31" t="n">
-        <v>88992</v>
+        <v>57736</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R31" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3575,6 +3575,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3604,7 +3609,7 @@
         <v>129827146</v>
       </c>
       <c r="B32" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827162</v>
+        <v>129827141</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>91597</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574844</v>
+        <v>574904</v>
       </c>
       <c r="R33" t="n">
-        <v>7071940</v>
+        <v>7071706</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,41 +3800,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827196</v>
+        <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91613</v>
+        <v>91810</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574833</v>
+        <v>574908</v>
       </c>
       <c r="R34" t="n">
-        <v>7071729</v>
+        <v>7071708</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3875,6 +3882,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3893,48 +3901,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129835984</v>
+        <v>129827196</v>
       </c>
       <c r="B35" t="n">
-        <v>91806</v>
+        <v>91617</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574908</v>
+        <v>574833</v>
       </c>
       <c r="R35" t="n">
-        <v>7071708</v>
+        <v>7071729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3975,7 +3976,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B38" t="n">
-        <v>92284</v>
+        <v>57736</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,6 +4269,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>92288</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,10 +4397,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827185</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,21 +4408,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>574754</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4497,7 +4497,7 @@
         <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>92046</v>
+        <v>92050</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91593</v>
+        <v>91597</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R2" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R3" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827138</v>
+        <v>129827192</v>
       </c>
       <c r="B7" t="n">
-        <v>91597</v>
+        <v>80186</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574868</v>
+        <v>574881</v>
       </c>
       <c r="R7" t="n">
-        <v>7071732</v>
+        <v>7071589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B8" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R8" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827156</v>
+        <v>129827138</v>
       </c>
       <c r="B9" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574917</v>
+        <v>574868</v>
       </c>
       <c r="R9" t="n">
-        <v>7071640</v>
+        <v>7071732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827187</v>
+        <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>80186</v>
+        <v>92322</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575013</v>
+        <v>575031</v>
       </c>
       <c r="R10" t="n">
-        <v>7071709</v>
+        <v>7071787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1553,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827176</v>
+        <v>129827187</v>
       </c>
       <c r="B11" t="n">
-        <v>92320</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575031</v>
+        <v>575013</v>
       </c>
       <c r="R11" t="n">
-        <v>7071787</v>
+        <v>7071709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,7 +1633,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>129827199</v>
       </c>
       <c r="B14" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827188</v>
+        <v>129827174</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574912</v>
+        <v>574764</v>
       </c>
       <c r="R20" t="n">
-        <v>7071745</v>
+        <v>7071692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,6 +2503,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827188</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574912</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071745</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2731,7 +2731,7 @@
         <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>92288</v>
+        <v>92290</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3313,7 +3313,7 @@
         <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>91895</v>
+        <v>91897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3410,7 +3410,7 @@
         <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>88996</v>
+        <v>88998</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827162</v>
+        <v>129827146</v>
       </c>
       <c r="B31" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574844</v>
+        <v>574908</v>
       </c>
       <c r="R31" t="n">
-        <v>7071940</v>
+        <v>7071600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3575,11 +3575,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3606,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827146</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574908</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071600</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827141</v>
+        <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>91597</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574904</v>
+        <v>574844</v>
       </c>
       <c r="R33" t="n">
-        <v>7071706</v>
+        <v>7071940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3803,7 +3803,7 @@
         <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91810</v>
+        <v>91812</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>129827196</v>
       </c>
       <c r="B35" t="n">
-        <v>91617</v>
+        <v>91619</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827171</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>57736</v>
+        <v>92290</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574903</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071393</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,11 +4269,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B39" t="n">
-        <v>92288</v>
+        <v>80186</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R39" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4397,10 +4392,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827185</v>
+        <v>129827171</v>
       </c>
       <c r="B40" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4408,21 +4403,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574754</v>
+        <v>574903</v>
       </c>
       <c r="R40" t="n">
-        <v>7071844</v>
+        <v>7071393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,6 +4463,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4497,7 +4497,7 @@
         <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>92050</v>
+        <v>92052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4696,7 +4696,7 @@
         <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91597</v>
+        <v>91599</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R2" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R3" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827160</v>
+        <v>129827194</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574930</v>
+        <v>574878</v>
       </c>
       <c r="R19" t="n">
-        <v>7071643</v>
+        <v>7071591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827174</v>
+        <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574764</v>
+        <v>574912</v>
       </c>
       <c r="R20" t="n">
-        <v>7071692</v>
+        <v>7071745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,11 +2503,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2534,10 +2529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827160</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2545,21 +2540,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574930</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2631,10 +2626,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827188</v>
+        <v>129827174</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2637,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574912</v>
+        <v>574764</v>
       </c>
       <c r="R22" t="n">
-        <v>7071745</v>
+        <v>7071692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2702,6 +2697,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R41" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R42" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827194</v>
+        <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574878</v>
+        <v>574930</v>
       </c>
       <c r="R19" t="n">
-        <v>7071591</v>
+        <v>7071643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827188</v>
+        <v>129827174</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574912</v>
+        <v>574764</v>
       </c>
       <c r="R20" t="n">
-        <v>7071745</v>
+        <v>7071692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,6 +2503,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2529,10 +2534,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827160</v>
+        <v>129827194</v>
       </c>
       <c r="B21" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2540,21 +2545,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574930</v>
+        <v>574878</v>
       </c>
       <c r="R21" t="n">
-        <v>7071643</v>
+        <v>7071591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827188</v>
       </c>
       <c r="B22" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574912</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071745</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827162</v>
       </c>
       <c r="B29" t="n">
-        <v>91897</v>
+        <v>57736</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574844</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,6 +3381,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3407,10 +3412,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827197</v>
+        <v>129827146</v>
       </c>
       <c r="B30" t="n">
-        <v>88998</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3423,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574842</v>
+        <v>574908</v>
       </c>
       <c r="R30" t="n">
-        <v>7071778</v>
+        <v>7071600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,7 +3509,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827146</v>
+        <v>129827141</v>
       </c>
       <c r="B31" t="n">
         <v>91599</v>
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574908</v>
+        <v>574904</v>
       </c>
       <c r="R31" t="n">
-        <v>7071600</v>
+        <v>7071706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827141</v>
+        <v>129827183</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>91897</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574904</v>
+        <v>574913</v>
       </c>
       <c r="R32" t="n">
-        <v>7071706</v>
+        <v>7071700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827162</v>
+        <v>129827197</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>88998</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574844</v>
+        <v>574842</v>
       </c>
       <c r="R33" t="n">
-        <v>7071940</v>
+        <v>7071778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827162</v>
+        <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>57736</v>
+        <v>91897</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574844</v>
+        <v>574913</v>
       </c>
       <c r="R29" t="n">
-        <v>7071940</v>
+        <v>7071700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,11 +3381,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3412,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827146</v>
+        <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>88998</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574908</v>
+        <v>574842</v>
       </c>
       <c r="R30" t="n">
-        <v>7071600</v>
+        <v>7071778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827141</v>
+        <v>129827146</v>
       </c>
       <c r="B31" t="n">
         <v>91599</v>
@@ -3544,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574904</v>
+        <v>574908</v>
       </c>
       <c r="R31" t="n">
-        <v>7071706</v>
+        <v>7071600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>91897</v>
+        <v>91599</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>88998</v>
+        <v>57736</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R33" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R2" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R3" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B7" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R7" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827156</v>
+        <v>129827138</v>
       </c>
       <c r="B8" t="n">
         <v>91599</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574917</v>
+        <v>574868</v>
       </c>
       <c r="R8" t="n">
-        <v>7071640</v>
+        <v>7071732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827138</v>
+        <v>129827192</v>
       </c>
       <c r="B9" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574868</v>
+        <v>574881</v>
       </c>
       <c r="R9" t="n">
-        <v>7071732</v>
+        <v>7071589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827137</v>
+        <v>129827165</v>
       </c>
       <c r="B16" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574860</v>
+        <v>575010</v>
       </c>
       <c r="R16" t="n">
-        <v>7071793</v>
+        <v>7071669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,6 +2110,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2136,7 +2141,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827149</v>
+        <v>129827137</v>
       </c>
       <c r="B17" t="n">
         <v>91599</v>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574910</v>
+        <v>574860</v>
       </c>
       <c r="R17" t="n">
-        <v>7071608</v>
+        <v>7071793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,10 +2238,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827165</v>
+        <v>129827149</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2249,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2273,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575010</v>
+        <v>574910</v>
       </c>
       <c r="R18" t="n">
-        <v>7071669</v>
+        <v>7071608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2304,11 +2309,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B19" t="n">
-        <v>91599</v>
+        <v>57736</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R19" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,6 +2406,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2432,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827174</v>
+        <v>129827160</v>
       </c>
       <c r="B20" t="n">
-        <v>57736</v>
+        <v>91599</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574764</v>
+        <v>574930</v>
       </c>
       <c r="R20" t="n">
-        <v>7071692</v>
+        <v>7071643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,11 +2508,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>92290</v>
+        <v>91599</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R23" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>91599</v>
+        <v>92290</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R24" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827197</v>
+        <v>129827146</v>
       </c>
       <c r="B30" t="n">
-        <v>88998</v>
+        <v>91599</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574842</v>
+        <v>574908</v>
       </c>
       <c r="R30" t="n">
-        <v>7071778</v>
+        <v>7071600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,7 +3504,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827146</v>
+        <v>129827141</v>
       </c>
       <c r="B31" t="n">
         <v>91599</v>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574908</v>
+        <v>574904</v>
       </c>
       <c r="R31" t="n">
-        <v>7071600</v>
+        <v>7071706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B32" t="n">
-        <v>91599</v>
+        <v>88998</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R32" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,48 +3800,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835984</v>
+        <v>129827196</v>
       </c>
       <c r="B34" t="n">
-        <v>91812</v>
+        <v>91619</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574908</v>
+        <v>574833</v>
       </c>
       <c r="R34" t="n">
-        <v>7071708</v>
+        <v>7071729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3882,7 +3875,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3901,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827196</v>
+        <v>129827164</v>
       </c>
       <c r="B35" t="n">
-        <v>91619</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,19 +3904,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3932,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574833</v>
+        <v>574945</v>
       </c>
       <c r="R35" t="n">
-        <v>7071729</v>
+        <v>7071651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3968,6 +3964,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,7 +3995,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827164</v>
+        <v>129827167</v>
       </c>
       <c r="B36" t="n">
         <v>57736</v>
@@ -4029,10 +4030,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574945</v>
+        <v>574886</v>
       </c>
       <c r="R36" t="n">
-        <v>7071651</v>
+        <v>7071594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4096,45 +4097,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827167</v>
+        <v>129835984</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>91812</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574886</v>
+        <v>574908</v>
       </c>
       <c r="R37" t="n">
-        <v>7071594</v>
+        <v>7071708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4169,17 +4173,13 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R41" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,32 +4591,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B42" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R42" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B11" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B19" t="n">
-        <v>57736</v>
+        <v>80186</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R19" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,11 +2406,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827160</v>
+        <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>91599</v>
+        <v>80186</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574930</v>
+        <v>574912</v>
       </c>
       <c r="R20" t="n">
-        <v>7071643</v>
+        <v>7071745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,10 +2529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827174</v>
       </c>
       <c r="B21" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2545,21 +2540,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574764</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071692</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2605,6 +2600,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2631,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827188</v>
+        <v>129827160</v>
       </c>
       <c r="B22" t="n">
-        <v>80186</v>
+        <v>91599</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574912</v>
+        <v>574930</v>
       </c>
       <c r="R22" t="n">
-        <v>7071745</v>
+        <v>7071643</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B38" t="n">
-        <v>92290</v>
+        <v>80186</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827171</v>
       </c>
       <c r="B39" t="n">
-        <v>80186</v>
+        <v>57736</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574903</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4392,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827204</v>
       </c>
       <c r="B40" t="n">
-        <v>57736</v>
+        <v>92290</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>574932</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071642</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>92052</v>
+        <v>57736</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R41" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>57736</v>
+        <v>92052</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R42" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129827156</v>
       </c>
       <c r="B7" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129827138</v>
       </c>
       <c r="B8" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1362,7 +1362,7 @@
         <v>129827192</v>
       </c>
       <c r="B9" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>92322</v>
+        <v>92325</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129827187</v>
       </c>
       <c r="B11" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1654,7 +1654,7 @@
         <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>129827190</v>
       </c>
       <c r="B13" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>129827199</v>
       </c>
       <c r="B14" t="n">
-        <v>88998</v>
+        <v>89001</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827165</v>
+        <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>57736</v>
+        <v>91602</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575010</v>
+        <v>574860</v>
       </c>
       <c r="R16" t="n">
-        <v>7071669</v>
+        <v>7071793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,11 +2110,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2141,10 +2136,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827137</v>
+        <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574860</v>
+        <v>574910</v>
       </c>
       <c r="R17" t="n">
-        <v>7071793</v>
+        <v>7071608</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827149</v>
+        <v>129827165</v>
       </c>
       <c r="B18" t="n">
-        <v>91599</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2249,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2273,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574910</v>
+        <v>575010</v>
       </c>
       <c r="R18" t="n">
-        <v>7071608</v>
+        <v>7071669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2309,6 +2304,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827194</v>
+        <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>80186</v>
+        <v>91602</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574878</v>
+        <v>574930</v>
       </c>
       <c r="R19" t="n">
-        <v>7071591</v>
+        <v>7071643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2435,7 +2435,7 @@
         <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>80186</v>
+        <v>80189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2529,10 +2529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B21" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2540,21 +2540,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2564,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R21" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2600,11 +2600,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2631,10 +2626,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B22" t="n">
-        <v>91599</v>
+        <v>57737</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2637,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R22" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2702,6 +2697,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2731,7 +2731,7 @@
         <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>92290</v>
+        <v>92293</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92052</v>
+        <v>92055</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827197</v>
       </c>
       <c r="B29" t="n">
-        <v>91897</v>
+        <v>89001</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>510</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574842</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071778</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827146</v>
+        <v>129827183</v>
       </c>
       <c r="B30" t="n">
-        <v>91599</v>
+        <v>91900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574908</v>
+        <v>574913</v>
       </c>
       <c r="R30" t="n">
-        <v>7071600</v>
+        <v>7071700</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827141</v>
+        <v>129827146</v>
       </c>
       <c r="B31" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574904</v>
+        <v>574908</v>
       </c>
       <c r="R31" t="n">
-        <v>7071706</v>
+        <v>7071600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827197</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>88998</v>
+        <v>91602</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574842</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071778</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
         <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3800,41 +3800,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827196</v>
+        <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91619</v>
+        <v>91815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574833</v>
+        <v>574908</v>
       </c>
       <c r="R34" t="n">
-        <v>7071729</v>
+        <v>7071708</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3875,6 +3882,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3893,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827164</v>
+        <v>129827196</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>91622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,23 +3912,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3928,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574945</v>
+        <v>574833</v>
       </c>
       <c r="R35" t="n">
-        <v>7071651</v>
+        <v>7071729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3964,11 +3968,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3995,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827167</v>
+        <v>129827164</v>
       </c>
       <c r="B36" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574886</v>
+        <v>574945</v>
       </c>
       <c r="R36" t="n">
-        <v>7071594</v>
+        <v>7071651</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4097,48 +4096,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129835984</v>
+        <v>129827167</v>
       </c>
       <c r="B37" t="n">
-        <v>91812</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574908</v>
+        <v>574886</v>
       </c>
       <c r="R37" t="n">
-        <v>7071708</v>
+        <v>7071594</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4173,13 +4169,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>80186</v>
+        <v>92293</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827171</v>
+        <v>129827185</v>
       </c>
       <c r="B39" t="n">
-        <v>57736</v>
+        <v>80189</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574903</v>
+        <v>574754</v>
       </c>
       <c r="R39" t="n">
-        <v>7071393</v>
+        <v>7071844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,11 +4366,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4397,32 +4392,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B40" t="n">
-        <v>92290</v>
+        <v>57737</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R40" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,6 +4463,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>57736</v>
+        <v>92055</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R41" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,32 +4591,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B42" t="n">
-        <v>92052</v>
+        <v>57737</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R42" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4696,7 +4696,7 @@
         <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91599</v>
+        <v>91602</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1554,10 +1554,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>80189</v>
+        <v>91602</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1565,21 +1565,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>80189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B19" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R19" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,6 +2406,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2432,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827188</v>
+        <v>129827160</v>
       </c>
       <c r="B20" t="n">
-        <v>80189</v>
+        <v>91602</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574912</v>
+        <v>574930</v>
       </c>
       <c r="R20" t="n">
-        <v>7071745</v>
+        <v>7071643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2529,7 +2534,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827188</v>
       </c>
       <c r="B21" t="n">
         <v>80189</v>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574912</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2922,7 +2922,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129827126</v>
+        <v>129827130</v>
       </c>
       <c r="B25" t="n">
         <v>91602</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574962</v>
+        <v>574900</v>
       </c>
       <c r="R25" t="n">
-        <v>7071877</v>
+        <v>7071911</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129827130</v>
+        <v>129827126</v>
       </c>
       <c r="B26" t="n">
         <v>91602</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574900</v>
+        <v>574962</v>
       </c>
       <c r="R26" t="n">
-        <v>7071911</v>
+        <v>7071877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827197</v>
+        <v>129827146</v>
       </c>
       <c r="B29" t="n">
-        <v>89001</v>
+        <v>91602</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574842</v>
+        <v>574908</v>
       </c>
       <c r="R29" t="n">
-        <v>7071778</v>
+        <v>7071600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B30" t="n">
-        <v>91900</v>
+        <v>91602</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R30" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827146</v>
+        <v>129827183</v>
       </c>
       <c r="B31" t="n">
-        <v>91602</v>
+        <v>91900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574908</v>
+        <v>574913</v>
       </c>
       <c r="R31" t="n">
-        <v>7071600</v>
+        <v>7071700</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B32" t="n">
-        <v>91602</v>
+        <v>89001</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R32" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,48 +3800,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835984</v>
+        <v>129827196</v>
       </c>
       <c r="B34" t="n">
-        <v>91815</v>
+        <v>91622</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574908</v>
+        <v>574833</v>
       </c>
       <c r="R34" t="n">
-        <v>7071708</v>
+        <v>7071729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3882,7 +3875,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3901,10 +3893,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827196</v>
+        <v>129827164</v>
       </c>
       <c r="B35" t="n">
-        <v>91622</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,19 +3904,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3932,10 +3928,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574833</v>
+        <v>574945</v>
       </c>
       <c r="R35" t="n">
-        <v>7071729</v>
+        <v>7071651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3968,6 +3964,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,7 +3995,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827164</v>
+        <v>129827167</v>
       </c>
       <c r="B36" t="n">
         <v>57737</v>
@@ -4029,10 +4030,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574945</v>
+        <v>574886</v>
       </c>
       <c r="R36" t="n">
-        <v>7071651</v>
+        <v>7071594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4096,45 +4097,48 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827167</v>
+        <v>129835984</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>91815</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574886</v>
+        <v>574908</v>
       </c>
       <c r="R37" t="n">
-        <v>7071594</v>
+        <v>7071708</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4169,17 +4173,13 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827124</v>
+        <v>129827143</v>
       </c>
       <c r="B43" t="n">
         <v>91602</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575029</v>
+        <v>574888</v>
       </c>
       <c r="R43" t="n">
-        <v>7071789</v>
+        <v>7071636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129827143</v>
+        <v>129827124</v>
       </c>
       <c r="B44" t="n">
         <v>91602</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574888</v>
+        <v>575029</v>
       </c>
       <c r="R44" t="n">
-        <v>7071636</v>
+        <v>7071789</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827187</v>
       </c>
       <c r="B10" t="n">
-        <v>92325</v>
+        <v>80189</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>575013</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,7 +1535,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B11" t="n">
-        <v>91602</v>
+        <v>92325</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1632,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80189</v>
+        <v>91602</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827137</v>
+        <v>129827165</v>
       </c>
       <c r="B16" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574860</v>
+        <v>575010</v>
       </c>
       <c r="R16" t="n">
-        <v>7071793</v>
+        <v>7071669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,6 +2110,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2136,7 +2141,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827149</v>
+        <v>129827137</v>
       </c>
       <c r="B17" t="n">
         <v>91602</v>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574910</v>
+        <v>574860</v>
       </c>
       <c r="R17" t="n">
-        <v>7071608</v>
+        <v>7071793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,10 +2238,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827165</v>
+        <v>129827149</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>91602</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2249,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2273,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575010</v>
+        <v>574910</v>
       </c>
       <c r="R18" t="n">
-        <v>7071669</v>
+        <v>7071608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2304,11 +2309,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>91602</v>
+        <v>92293</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R23" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>92293</v>
+        <v>91602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R24" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129827130</v>
+        <v>129827126</v>
       </c>
       <c r="B25" t="n">
         <v>91602</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574900</v>
+        <v>574962</v>
       </c>
       <c r="R25" t="n">
-        <v>7071911</v>
+        <v>7071877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129827126</v>
+        <v>129827130</v>
       </c>
       <c r="B26" t="n">
         <v>91602</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574962</v>
+        <v>574900</v>
       </c>
       <c r="R26" t="n">
-        <v>7071877</v>
+        <v>7071911</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827146</v>
+        <v>129827162</v>
       </c>
       <c r="B29" t="n">
-        <v>91602</v>
+        <v>57737</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574908</v>
+        <v>574844</v>
       </c>
       <c r="R29" t="n">
-        <v>7071600</v>
+        <v>7071940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,6 +3381,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3504,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827183</v>
+        <v>129827146</v>
       </c>
       <c r="B31" t="n">
-        <v>91900</v>
+        <v>91602</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574913</v>
+        <v>574908</v>
       </c>
       <c r="R31" t="n">
-        <v>7071700</v>
+        <v>7071600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827197</v>
+        <v>129827183</v>
       </c>
       <c r="B32" t="n">
-        <v>89001</v>
+        <v>91900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574842</v>
+        <v>574913</v>
       </c>
       <c r="R32" t="n">
-        <v>7071778</v>
+        <v>7071700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827162</v>
+        <v>129827197</v>
       </c>
       <c r="B33" t="n">
-        <v>57737</v>
+        <v>89001</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574844</v>
+        <v>574842</v>
       </c>
       <c r="R33" t="n">
-        <v>7071940</v>
+        <v>7071778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,41 +3800,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827196</v>
+        <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91622</v>
+        <v>91815</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574833</v>
+        <v>574908</v>
       </c>
       <c r="R34" t="n">
-        <v>7071729</v>
+        <v>7071708</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3875,6 +3882,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3893,10 +3901,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827164</v>
+        <v>129827196</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>91622</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3904,23 +3912,19 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3928,10 +3932,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574945</v>
+        <v>574833</v>
       </c>
       <c r="R35" t="n">
-        <v>7071651</v>
+        <v>7071729</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3964,11 +3968,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4097,48 +4096,45 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129835984</v>
+        <v>129827164</v>
       </c>
       <c r="B37" t="n">
-        <v>91815</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574908</v>
+        <v>574945</v>
       </c>
       <c r="R37" t="n">
-        <v>7071708</v>
+        <v>7071651</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4173,13 +4169,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
         <v>0</v>
       </c>
-      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B38" t="n">
-        <v>92293</v>
+        <v>57737</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,6 +4269,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B39" t="n">
-        <v>80189</v>
+        <v>92293</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,10 +4397,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827185</v>
       </c>
       <c r="B40" t="n">
-        <v>57737</v>
+        <v>80189</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,21 +4408,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>574754</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>92055</v>
+        <v>57737</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R41" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>57737</v>
+        <v>92055</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R42" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4693,7 +4693,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827143</v>
+        <v>129827124</v>
       </c>
       <c r="B43" t="n">
         <v>91602</v>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574888</v>
+        <v>575029</v>
       </c>
       <c r="R43" t="n">
-        <v>7071636</v>
+        <v>7071789</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4790,7 +4790,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129827124</v>
+        <v>129827143</v>
       </c>
       <c r="B44" t="n">
         <v>91602</v>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575029</v>
+        <v>574888</v>
       </c>
       <c r="R44" t="n">
-        <v>7071789</v>
+        <v>7071636</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B2" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R2" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B3" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R3" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91900</v>
+        <v>91903</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827156</v>
+        <v>129827192</v>
       </c>
       <c r="B7" t="n">
-        <v>91602</v>
+        <v>80192</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574917</v>
+        <v>574881</v>
       </c>
       <c r="R7" t="n">
-        <v>7071640</v>
+        <v>7071589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827138</v>
+        <v>129827156</v>
       </c>
       <c r="B8" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574868</v>
+        <v>574917</v>
       </c>
       <c r="R8" t="n">
-        <v>7071732</v>
+        <v>7071640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827192</v>
+        <v>129827138</v>
       </c>
       <c r="B9" t="n">
-        <v>80189</v>
+        <v>91605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574881</v>
+        <v>574868</v>
       </c>
       <c r="R9" t="n">
-        <v>7071589</v>
+        <v>7071732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827187</v>
+        <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>80189</v>
+        <v>92328</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575013</v>
+        <v>575031</v>
       </c>
       <c r="R10" t="n">
-        <v>7071709</v>
+        <v>7071787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1553,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827176</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>92325</v>
+        <v>91605</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575031</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071787</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,7 +1633,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91602</v>
+        <v>80192</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
         <v>129827190</v>
       </c>
       <c r="B13" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>129827199</v>
       </c>
       <c r="B14" t="n">
-        <v>89001</v>
+        <v>89004</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827165</v>
+        <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>575010</v>
+        <v>574860</v>
       </c>
       <c r="R16" t="n">
-        <v>7071669</v>
+        <v>7071793</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,11 +2110,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2141,10 +2136,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827137</v>
+        <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2176,10 +2171,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574860</v>
+        <v>574910</v>
       </c>
       <c r="R17" t="n">
-        <v>7071793</v>
+        <v>7071608</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2238,10 +2233,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827149</v>
+        <v>129827165</v>
       </c>
       <c r="B18" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2249,21 +2244,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2273,10 +2268,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>574910</v>
+        <v>575010</v>
       </c>
       <c r="R18" t="n">
-        <v>7071608</v>
+        <v>7071669</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2309,6 +2304,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827174</v>
+        <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>57737</v>
+        <v>91605</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574764</v>
+        <v>574930</v>
       </c>
       <c r="R19" t="n">
-        <v>7071692</v>
+        <v>7071643</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,11 +2406,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B20" t="n">
-        <v>91602</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R20" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2508,6 +2503,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2537,7 +2537,7 @@
         <v>129827188</v>
       </c>
       <c r="B21" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>92293</v>
+        <v>92296</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2922,10 +2922,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129827126</v>
+        <v>129827130</v>
       </c>
       <c r="B25" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574962</v>
+        <v>574900</v>
       </c>
       <c r="R25" t="n">
-        <v>7071877</v>
+        <v>7071911</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3019,10 +3019,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129827130</v>
+        <v>129827126</v>
       </c>
       <c r="B26" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574900</v>
+        <v>574962</v>
       </c>
       <c r="R26" t="n">
-        <v>7071911</v>
+        <v>7071877</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92055</v>
+        <v>92058</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827162</v>
+        <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>57737</v>
+        <v>91903</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574844</v>
+        <v>574913</v>
       </c>
       <c r="R29" t="n">
-        <v>7071940</v>
+        <v>7071700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,11 +3381,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3412,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>91602</v>
+        <v>89004</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R30" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3512,7 +3507,7 @@
         <v>129827146</v>
       </c>
       <c r="B31" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3606,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>91900</v>
+        <v>91605</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>89001</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R33" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3803,7 +3803,7 @@
         <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91815</v>
+        <v>91818</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>129827196</v>
       </c>
       <c r="B35" t="n">
-        <v>91622</v>
+        <v>91625</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3994,10 +3994,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827167</v>
+        <v>129827164</v>
       </c>
       <c r="B36" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4029,10 +4029,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574886</v>
+        <v>574945</v>
       </c>
       <c r="R36" t="n">
-        <v>7071594</v>
+        <v>7071651</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4096,10 +4096,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827164</v>
+        <v>129827167</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4131,10 +4131,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574945</v>
+        <v>574886</v>
       </c>
       <c r="R37" t="n">
-        <v>7071651</v>
+        <v>7071594</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827171</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>57737</v>
+        <v>92296</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574903</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071393</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,11 +4269,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4300,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B39" t="n">
-        <v>92293</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4335,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R39" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4371,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4400,7 +4400,7 @@
         <v>129827185</v>
       </c>
       <c r="B40" t="n">
-        <v>80189</v>
+        <v>80192</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>57737</v>
+        <v>92058</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R41" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,32 +4591,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B42" t="n">
-        <v>92055</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R42" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4696,7 +4696,7 @@
         <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91602</v>
+        <v>91605</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R2" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>57740</v>
+        <v>91605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R3" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827131</v>
       </c>
       <c r="B10" t="n">
-        <v>92328</v>
+        <v>91605</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>574994</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071732</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,7 +1535,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B11" t="n">
-        <v>91605</v>
+        <v>92328</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1632,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>92296</v>
+        <v>91605</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R23" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>91605</v>
+        <v>92296</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R24" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2922,7 +2922,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129827130</v>
+        <v>129827126</v>
       </c>
       <c r="B25" t="n">
         <v>91605</v>
@@ -2957,10 +2957,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574900</v>
+        <v>574962</v>
       </c>
       <c r="R25" t="n">
-        <v>7071911</v>
+        <v>7071877</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3019,7 +3019,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129827126</v>
+        <v>129827130</v>
       </c>
       <c r="B26" t="n">
         <v>91605</v>
@@ -3054,10 +3054,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574962</v>
+        <v>574900</v>
       </c>
       <c r="R26" t="n">
-        <v>7071877</v>
+        <v>7071911</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B2" t="n">
-        <v>57740</v>
+        <v>91606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R2" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,11 +746,6 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B3" t="n">
-        <v>91605</v>
+        <v>57740</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -788,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R3" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -848,6 +843,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129827151</v>
+        <v>129827135</v>
       </c>
       <c r="B4" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574914</v>
+        <v>574871</v>
       </c>
       <c r="R4" t="n">
-        <v>7071623</v>
+        <v>7071853</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129827135</v>
+        <v>129827151</v>
       </c>
       <c r="B5" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574871</v>
+        <v>574914</v>
       </c>
       <c r="R5" t="n">
-        <v>7071853</v>
+        <v>7071623</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91903</v>
+        <v>91904</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B7" t="n">
-        <v>80192</v>
+        <v>91606</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R7" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827156</v>
+        <v>129827138</v>
       </c>
       <c r="B8" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574917</v>
+        <v>574868</v>
       </c>
       <c r="R8" t="n">
-        <v>7071640</v>
+        <v>7071732</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827138</v>
+        <v>129827192</v>
       </c>
       <c r="B9" t="n">
-        <v>91605</v>
+        <v>80193</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574868</v>
+        <v>574881</v>
       </c>
       <c r="R9" t="n">
-        <v>7071732</v>
+        <v>7071589</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>91605</v>
+        <v>92329</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R10" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1553,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827176</v>
+        <v>129827187</v>
       </c>
       <c r="B11" t="n">
-        <v>92328</v>
+        <v>80193</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575031</v>
+        <v>575013</v>
       </c>
       <c r="R11" t="n">
-        <v>7071787</v>
+        <v>7071709</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,7 +1633,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80192</v>
+        <v>91606</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
         <v>129827190</v>
       </c>
       <c r="B13" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1848,7 +1848,7 @@
         <v>129827199</v>
       </c>
       <c r="B14" t="n">
-        <v>89004</v>
+        <v>89005</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827174</v>
+        <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574764</v>
+        <v>574912</v>
       </c>
       <c r="R20" t="n">
-        <v>7071692</v>
+        <v>7071745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,11 +2503,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2534,10 +2529,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827188</v>
+        <v>129827194</v>
       </c>
       <c r="B21" t="n">
-        <v>80192</v>
+        <v>80193</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2569,10 +2564,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574912</v>
+        <v>574878</v>
       </c>
       <c r="R21" t="n">
-        <v>7071745</v>
+        <v>7071591</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2631,10 +2626,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827194</v>
+        <v>129827174</v>
       </c>
       <c r="B22" t="n">
-        <v>80192</v>
+        <v>57740</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2637,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2661,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574878</v>
+        <v>574764</v>
       </c>
       <c r="R22" t="n">
-        <v>7071591</v>
+        <v>7071692</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2702,6 +2697,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>91605</v>
+        <v>92297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R23" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>92296</v>
+        <v>91606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R24" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,32 +3116,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129827153</v>
+        <v>129827178</v>
       </c>
       <c r="B27" t="n">
-        <v>91605</v>
+        <v>92059</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574910</v>
+        <v>574987</v>
       </c>
       <c r="R27" t="n">
-        <v>7071631</v>
+        <v>7071663</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129827178</v>
+        <v>129827153</v>
       </c>
       <c r="B28" t="n">
-        <v>92058</v>
+        <v>91606</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574987</v>
+        <v>574910</v>
       </c>
       <c r="R28" t="n">
-        <v>7071663</v>
+        <v>7071631</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827146</v>
       </c>
       <c r="B29" t="n">
-        <v>91903</v>
+        <v>91606</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574908</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827197</v>
+        <v>129827141</v>
       </c>
       <c r="B30" t="n">
-        <v>89004</v>
+        <v>91606</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574842</v>
+        <v>574904</v>
       </c>
       <c r="R30" t="n">
-        <v>7071778</v>
+        <v>7071706</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827146</v>
+        <v>129827183</v>
       </c>
       <c r="B31" t="n">
-        <v>91605</v>
+        <v>91904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3515,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574908</v>
+        <v>574913</v>
       </c>
       <c r="R31" t="n">
-        <v>7071600</v>
+        <v>7071700</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B32" t="n">
-        <v>91605</v>
+        <v>89005</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R32" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3800,48 +3800,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835984</v>
+        <v>129827196</v>
       </c>
       <c r="B34" t="n">
-        <v>91818</v>
+        <v>91626</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>5432</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574908</v>
+        <v>574833</v>
       </c>
       <c r="R34" t="n">
-        <v>7071708</v>
+        <v>7071729</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3882,7 +3875,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3901,41 +3893,48 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827196</v>
+        <v>129835984</v>
       </c>
       <c r="B35" t="n">
-        <v>91625</v>
+        <v>91819</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574833</v>
+        <v>574908</v>
       </c>
       <c r="R35" t="n">
-        <v>7071729</v>
+        <v>7071708</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3976,6 +3975,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B38" t="n">
-        <v>92296</v>
+        <v>80193</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4397,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B40" t="n">
-        <v>80192</v>
+        <v>92297</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R40" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4497,7 +4497,7 @@
         <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>92058</v>
+        <v>92059</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827124</v>
+        <v>129827143</v>
       </c>
       <c r="B43" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575029</v>
+        <v>574888</v>
       </c>
       <c r="R43" t="n">
-        <v>7071789</v>
+        <v>7071636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129827143</v>
+        <v>129827124</v>
       </c>
       <c r="B44" t="n">
-        <v>91605</v>
+        <v>91606</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574888</v>
+        <v>575029</v>
       </c>
       <c r="R44" t="n">
-        <v>7071636</v>
+        <v>7071789</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>92297</v>
+        <v>91606</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R23" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>91606</v>
+        <v>92297</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R24" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827146</v>
+        <v>129827162</v>
       </c>
       <c r="B29" t="n">
-        <v>91606</v>
+        <v>57740</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574908</v>
+        <v>574844</v>
       </c>
       <c r="R29" t="n">
-        <v>7071600</v>
+        <v>7071940</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,6 +3381,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3407,7 +3412,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827141</v>
+        <v>129827146</v>
       </c>
       <c r="B30" t="n">
         <v>91606</v>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574904</v>
+        <v>574908</v>
       </c>
       <c r="R30" t="n">
-        <v>7071706</v>
+        <v>7071600</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B31" t="n">
-        <v>91904</v>
+        <v>91606</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R31" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3601,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827197</v>
+        <v>129827183</v>
       </c>
       <c r="B32" t="n">
-        <v>89005</v>
+        <v>91904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3612,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>510</v>
+        <v>658</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3636,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574842</v>
+        <v>574913</v>
       </c>
       <c r="R32" t="n">
-        <v>7071778</v>
+        <v>7071700</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3698,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827162</v>
+        <v>129827197</v>
       </c>
       <c r="B33" t="n">
-        <v>57740</v>
+        <v>89005</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3709,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3733,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574844</v>
+        <v>574842</v>
       </c>
       <c r="R33" t="n">
-        <v>7071940</v>
+        <v>7071778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3769,11 +3774,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>80193</v>
+        <v>92297</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827171</v>
+        <v>129827185</v>
       </c>
       <c r="B39" t="n">
-        <v>57740</v>
+        <v>80193</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574903</v>
+        <v>574754</v>
       </c>
       <c r="R39" t="n">
-        <v>7071393</v>
+        <v>7071844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,11 +4366,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4397,32 +4392,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B40" t="n">
-        <v>92297</v>
+        <v>57740</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4432,10 +4427,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R40" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4468,6 +4463,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827131</v>
       </c>
       <c r="B10" t="n">
-        <v>92329</v>
+        <v>91606</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>574994</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071732</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,7 +1535,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827187</v>
+        <v>129827176</v>
       </c>
       <c r="B11" t="n">
-        <v>80193</v>
+        <v>92329</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575013</v>
+        <v>575031</v>
       </c>
       <c r="R11" t="n">
-        <v>7071709</v>
+        <v>7071787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1632,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827131</v>
+        <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>91606</v>
+        <v>80193</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>574994</v>
+        <v>575013</v>
       </c>
       <c r="R12" t="n">
-        <v>7071732</v>
+        <v>7071709</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B23" t="n">
-        <v>91606</v>
+        <v>92297</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R23" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B24" t="n">
-        <v>92297</v>
+        <v>91606</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R24" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>92059</v>
+        <v>57740</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R41" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>57740</v>
+        <v>92059</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R42" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129827158</v>
       </c>
       <c r="B2" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129827135</v>
+        <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574871</v>
+        <v>574914</v>
       </c>
       <c r="R4" t="n">
-        <v>7071853</v>
+        <v>7071623</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129827151</v>
+        <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574914</v>
+        <v>574871</v>
       </c>
       <c r="R5" t="n">
-        <v>7071623</v>
+        <v>7071853</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91904</v>
+        <v>91921</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827156</v>
+        <v>129827192</v>
       </c>
       <c r="B7" t="n">
-        <v>91606</v>
+        <v>80194</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574917</v>
+        <v>574881</v>
       </c>
       <c r="R7" t="n">
-        <v>7071640</v>
+        <v>7071589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827138</v>
+        <v>129827156</v>
       </c>
       <c r="B8" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574868</v>
+        <v>574917</v>
       </c>
       <c r="R8" t="n">
-        <v>7071732</v>
+        <v>7071640</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827192</v>
+        <v>129827138</v>
       </c>
       <c r="B9" t="n">
-        <v>80193</v>
+        <v>91623</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574881</v>
+        <v>574868</v>
       </c>
       <c r="R9" t="n">
-        <v>7071589</v>
+        <v>7071732</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>91606</v>
+        <v>92346</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R10" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,6 +1535,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1553,32 +1554,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827176</v>
+        <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>92329</v>
+        <v>91623</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>575031</v>
+        <v>574994</v>
       </c>
       <c r="R11" t="n">
-        <v>7071787</v>
+        <v>7071732</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1632,7 +1633,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>129827187</v>
       </c>
       <c r="B12" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1751,7 +1751,7 @@
         <v>129827190</v>
       </c>
       <c r="B13" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129827199</v>
+        <v>129827128</v>
       </c>
       <c r="B14" t="n">
-        <v>89005</v>
+        <v>91623</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574929</v>
+        <v>574950</v>
       </c>
       <c r="R14" t="n">
-        <v>7071646</v>
+        <v>7071890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129827128</v>
+        <v>129827199</v>
       </c>
       <c r="B15" t="n">
-        <v>91606</v>
+        <v>89022</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574950</v>
+        <v>574929</v>
       </c>
       <c r="R15" t="n">
-        <v>7071890</v>
+        <v>7071646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2042,7 +2042,7 @@
         <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>129827160</v>
       </c>
       <c r="B19" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2432,10 +2432,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827188</v>
+        <v>129827174</v>
       </c>
       <c r="B20" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574912</v>
+        <v>574764</v>
       </c>
       <c r="R20" t="n">
-        <v>7071745</v>
+        <v>7071692</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2503,6 +2503,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2529,10 +2534,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827188</v>
       </c>
       <c r="B21" t="n">
-        <v>80193</v>
+        <v>80194</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574912</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>57740</v>
+        <v>80194</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>92297</v>
+        <v>91623</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R23" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>91606</v>
+        <v>92314</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R24" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3116,32 +3116,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129827178</v>
+        <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>92059</v>
+        <v>91623</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3151,10 +3151,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574987</v>
+        <v>574910</v>
       </c>
       <c r="R27" t="n">
-        <v>7071663</v>
+        <v>7071631</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3213,32 +3213,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>129827153</v>
+        <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>91606</v>
+        <v>92076</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1202</v>
+        <v>1209</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3248,10 +3248,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>574910</v>
+        <v>574987</v>
       </c>
       <c r="R28" t="n">
-        <v>7071631</v>
+        <v>7071663</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827162</v>
+        <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>57740</v>
+        <v>91921</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574844</v>
+        <v>574913</v>
       </c>
       <c r="R29" t="n">
-        <v>7071940</v>
+        <v>7071700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3381,11 +3381,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3412,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827146</v>
+        <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>91606</v>
+        <v>89022</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3423,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3447,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574908</v>
+        <v>574842</v>
       </c>
       <c r="R30" t="n">
-        <v>7071600</v>
+        <v>7071778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3509,10 +3504,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827141</v>
+        <v>129827146</v>
       </c>
       <c r="B31" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3544,10 +3539,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574904</v>
+        <v>574908</v>
       </c>
       <c r="R31" t="n">
-        <v>7071706</v>
+        <v>7071600</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3606,10 +3601,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827183</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>91904</v>
+        <v>91623</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3612,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3636,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574913</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071700</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3698,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B33" t="n">
-        <v>89005</v>
+        <v>57740</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3709,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3733,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R33" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3774,6 +3769,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3800,41 +3800,48 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827196</v>
+        <v>129835984</v>
       </c>
       <c r="B34" t="n">
-        <v>91626</v>
+        <v>91836</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5432</v>
+        <v>48</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr"/>
+          <t>Amylocystis lapponica</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Romell) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574833</v>
+        <v>574908</v>
       </c>
       <c r="R34" t="n">
-        <v>7071729</v>
+        <v>7071708</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3875,6 +3882,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3893,48 +3901,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129835984</v>
+        <v>129827164</v>
       </c>
       <c r="B35" t="n">
-        <v>91819</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574908</v>
+        <v>574945</v>
       </c>
       <c r="R35" t="n">
-        <v>7071708</v>
+        <v>7071651</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3969,13 +3974,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -3994,7 +4003,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827164</v>
+        <v>129827167</v>
       </c>
       <c r="B36" t="n">
         <v>57740</v>
@@ -4029,10 +4038,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574945</v>
+        <v>574886</v>
       </c>
       <c r="R36" t="n">
-        <v>7071651</v>
+        <v>7071594</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4096,10 +4105,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827167</v>
+        <v>129827196</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>91643</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,23 +4116,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4131,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574886</v>
+        <v>574833</v>
       </c>
       <c r="R37" t="n">
-        <v>7071594</v>
+        <v>7071729</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,11 +4172,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B38" t="n">
-        <v>92297</v>
+        <v>80194</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,10 +4295,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827171</v>
       </c>
       <c r="B39" t="n">
-        <v>80193</v>
+        <v>57740</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4306,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574903</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071393</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,6 +4366,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4392,32 +4397,32 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827204</v>
       </c>
       <c r="B40" t="n">
-        <v>57740</v>
+        <v>92314</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>898</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>574932</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071642</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B41" t="n">
-        <v>57740</v>
+        <v>92076</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R41" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,11 +4565,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,32 +4591,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B42" t="n">
-        <v>92059</v>
+        <v>57740</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4631,10 +4626,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R42" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,6 +4662,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4693,10 +4693,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827143</v>
+        <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>574888</v>
+        <v>575029</v>
       </c>
       <c r="R43" t="n">
-        <v>7071636</v>
+        <v>7071789</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129827124</v>
+        <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91606</v>
+        <v>91623</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>575029</v>
+        <v>574888</v>
       </c>
       <c r="R44" t="n">
-        <v>7071789</v>
+        <v>7071636</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827158</v>
+        <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574924</v>
+        <v>574762</v>
       </c>
       <c r="R2" t="n">
-        <v>7071648</v>
+        <v>7071667</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -746,6 +746,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827173</v>
+        <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>57741</v>
+        <v>91641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -783,21 +788,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574762</v>
+        <v>574924</v>
       </c>
       <c r="R3" t="n">
-        <v>7071667</v>
+        <v>7071648</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -843,11 +848,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>129827156</v>
       </c>
       <c r="B7" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,7 +1265,7 @@
         <v>129827138</v>
       </c>
       <c r="B8" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129827176</v>
       </c>
       <c r="B10" t="n">
-        <v>92362</v>
+        <v>92364</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1557,7 +1557,7 @@
         <v>129827131</v>
       </c>
       <c r="B11" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>129827128</v>
       </c>
       <c r="B15" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>129827137</v>
       </c>
       <c r="B16" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>129827149</v>
       </c>
       <c r="B17" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2335,10 +2335,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827160</v>
+        <v>129827174</v>
       </c>
       <c r="B19" t="n">
-        <v>91639</v>
+        <v>57741</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2346,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574930</v>
+        <v>574764</v>
       </c>
       <c r="R19" t="n">
-        <v>7071643</v>
+        <v>7071692</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,6 +2406,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2432,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827188</v>
+        <v>129827160</v>
       </c>
       <c r="B20" t="n">
-        <v>80200</v>
+        <v>91641</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2443,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2467,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574912</v>
+        <v>574930</v>
       </c>
       <c r="R20" t="n">
-        <v>7071745</v>
+        <v>7071643</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2529,7 +2534,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827194</v>
+        <v>129827188</v>
       </c>
       <c r="B21" t="n">
         <v>80200</v>
@@ -2564,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574878</v>
+        <v>574912</v>
       </c>
       <c r="R21" t="n">
-        <v>7071591</v>
+        <v>7071745</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2626,10 +2631,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827174</v>
+        <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>57741</v>
+        <v>80200</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2637,21 +2642,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2661,10 +2666,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574764</v>
+        <v>574878</v>
       </c>
       <c r="R22" t="n">
-        <v>7071692</v>
+        <v>7071591</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2697,11 +2702,6 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2728,32 +2728,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827201</v>
+        <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>92330</v>
+        <v>91641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2763,10 +2763,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>575032</v>
+        <v>574988</v>
       </c>
       <c r="R23" t="n">
-        <v>7071788</v>
+        <v>7071665</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2825,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827133</v>
+        <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>91639</v>
+        <v>92332</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>574988</v>
+        <v>575032</v>
       </c>
       <c r="R24" t="n">
-        <v>7071665</v>
+        <v>7071788</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92092</v>
+        <v>92094</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827146</v>
+        <v>129827183</v>
       </c>
       <c r="B29" t="n">
-        <v>91639</v>
+        <v>91939</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574908</v>
+        <v>574913</v>
       </c>
       <c r="R29" t="n">
-        <v>7071600</v>
+        <v>7071700</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B30" t="n">
-        <v>91639</v>
+        <v>89038</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R30" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827183</v>
+        <v>129827146</v>
       </c>
       <c r="B32" t="n">
-        <v>91937</v>
+        <v>91641</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3617,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574913</v>
+        <v>574908</v>
       </c>
       <c r="R32" t="n">
-        <v>7071700</v>
+        <v>7071600</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827197</v>
+        <v>129827141</v>
       </c>
       <c r="B33" t="n">
-        <v>89038</v>
+        <v>91641</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574842</v>
+        <v>574904</v>
       </c>
       <c r="R33" t="n">
-        <v>7071778</v>
+        <v>7071706</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,48 +3800,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129835984</v>
+        <v>129827164</v>
       </c>
       <c r="B34" t="n">
-        <v>91852</v>
+        <v>57741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574908</v>
+        <v>574945</v>
       </c>
       <c r="R34" t="n">
-        <v>7071708</v>
+        <v>7071651</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3876,13 +3873,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -3901,10 +3902,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827196</v>
+        <v>129827167</v>
       </c>
       <c r="B35" t="n">
-        <v>91659</v>
+        <v>57741</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3912,19 +3913,23 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -3932,10 +3937,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574833</v>
+        <v>574886</v>
       </c>
       <c r="R35" t="n">
-        <v>7071729</v>
+        <v>7071594</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3968,6 +3973,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -3994,45 +4004,48 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129827164</v>
+        <v>129835984</v>
       </c>
       <c r="B36" t="n">
-        <v>57741</v>
+        <v>91854</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574945</v>
+        <v>574908</v>
       </c>
       <c r="R36" t="n">
-        <v>7071651</v>
+        <v>7071708</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4067,17 +4080,13 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
-        </is>
-      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
+      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4096,10 +4105,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827167</v>
+        <v>129827196</v>
       </c>
       <c r="B37" t="n">
-        <v>57741</v>
+        <v>91661</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4107,23 +4116,19 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4131,10 +4136,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574886</v>
+        <v>574833</v>
       </c>
       <c r="R37" t="n">
-        <v>7071594</v>
+        <v>7071729</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4167,11 +4172,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B38" t="n">
-        <v>80200</v>
+        <v>92332</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R38" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4295,32 +4295,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827204</v>
+        <v>129827185</v>
       </c>
       <c r="B39" t="n">
-        <v>92330</v>
+        <v>80200</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>898</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4330,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574932</v>
+        <v>574754</v>
       </c>
       <c r="R39" t="n">
-        <v>7071642</v>
+        <v>7071844</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4494,32 +4494,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827179</v>
+        <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>92092</v>
+        <v>57741</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4529,10 +4529,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>574866</v>
+        <v>575055</v>
       </c>
       <c r="R41" t="n">
-        <v>7071723</v>
+        <v>7071383</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4565,6 +4565,11 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4591,32 +4596,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827169</v>
+        <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>57741</v>
+        <v>92094</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4626,10 +4631,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>575055</v>
+        <v>574866</v>
       </c>
       <c r="R42" t="n">
-        <v>7071383</v>
+        <v>7071723</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4662,11 +4667,6 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4696,7 +4696,7 @@
         <v>129827124</v>
       </c>
       <c r="B43" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4793,7 +4793,7 @@
         <v>129827143</v>
       </c>
       <c r="B44" t="n">
-        <v>91639</v>
+        <v>91641</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129827173</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
         <v>129827158</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -877,7 +877,7 @@
         <v>129827151</v>
       </c>
       <c r="B4" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
         <v>129827135</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827156</v>
+        <v>129827192</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>80285</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574917</v>
+        <v>574881</v>
       </c>
       <c r="R7" t="n">
-        <v>7071640</v>
+        <v>7071589</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1265,7 +1265,7 @@
         <v>129827138</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1359,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827192</v>
+        <v>129827156</v>
       </c>
       <c r="B9" t="n">
-        <v>80200</v>
+        <v>91728</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574881</v>
+        <v>574917</v>
       </c>
       <c r="R9" t="n">
-        <v>7071589</v>
+        <v>7071640</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827187</v>
       </c>
       <c r="B10" t="n">
-        <v>92364</v>
+        <v>80285</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>575013</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071709</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1535,7 +1535,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,32 +1553,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827176</v>
       </c>
       <c r="B11" t="n">
-        <v>91641</v>
+        <v>92451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>575031</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071787</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1633,6 +1632,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1651,10 +1651,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827131</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>91728</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1662,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1686,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574994</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071732</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1751,7 +1751,7 @@
         <v>129827190</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,10 +1845,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129827199</v>
+        <v>129827128</v>
       </c>
       <c r="B14" t="n">
-        <v>89038</v>
+        <v>91728</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1856,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1880,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574929</v>
+        <v>574950</v>
       </c>
       <c r="R14" t="n">
-        <v>7071646</v>
+        <v>7071890</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,10 +1942,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129827128</v>
+        <v>129827199</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>89125</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1953,21 +1953,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1977,10 +1977,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574950</v>
+        <v>574929</v>
       </c>
       <c r="R15" t="n">
-        <v>7071890</v>
+        <v>7071646</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,10 +2039,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827137</v>
+        <v>129827165</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>57826</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2050,21 +2050,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2074,10 +2074,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574860</v>
+        <v>575010</v>
       </c>
       <c r="R16" t="n">
-        <v>7071793</v>
+        <v>7071669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2110,6 +2110,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2136,10 +2141,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827149</v>
+        <v>129827137</v>
       </c>
       <c r="B17" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,10 +2176,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574910</v>
+        <v>574860</v>
       </c>
       <c r="R17" t="n">
-        <v>7071608</v>
+        <v>7071793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,10 +2238,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827165</v>
+        <v>129827149</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>91728</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2249,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2273,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575010</v>
+        <v>574910</v>
       </c>
       <c r="R18" t="n">
-        <v>7071669</v>
+        <v>7071608</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2304,11 +2309,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2338,7 +2338,7 @@
         <v>129827174</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2437,10 +2437,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827160</v>
+        <v>129827188</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>80285</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2448,21 +2448,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2472,10 +2472,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574930</v>
+        <v>574912</v>
       </c>
       <c r="R20" t="n">
-        <v>7071643</v>
+        <v>7071745</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,10 +2534,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827188</v>
+        <v>129827160</v>
       </c>
       <c r="B21" t="n">
-        <v>80200</v>
+        <v>91728</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2545,21 +2545,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2569,10 +2569,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574912</v>
+        <v>574930</v>
       </c>
       <c r="R21" t="n">
-        <v>7071745</v>
+        <v>7071643</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2634,7 +2634,7 @@
         <v>129827194</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>80285</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2731,7 +2731,7 @@
         <v>129827133</v>
       </c>
       <c r="B23" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2828,7 +2828,7 @@
         <v>129827201</v>
       </c>
       <c r="B24" t="n">
-        <v>92332</v>
+        <v>92419</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2925,7 +2925,7 @@
         <v>129827126</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3022,7 +3022,7 @@
         <v>129827130</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3119,7 +3119,7 @@
         <v>129827153</v>
       </c>
       <c r="B27" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3216,7 +3216,7 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3310,10 +3310,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827146</v>
       </c>
       <c r="B29" t="n">
-        <v>91939</v>
+        <v>91728</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3321,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3345,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574908</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071600</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3407,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827197</v>
+        <v>129827162</v>
       </c>
       <c r="B30" t="n">
-        <v>89038</v>
+        <v>57826</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3418,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3442,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574842</v>
+        <v>574844</v>
       </c>
       <c r="R30" t="n">
-        <v>7071778</v>
+        <v>7071940</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3478,6 +3478,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3504,10 +3509,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827162</v>
+        <v>129827183</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>92026</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3520,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3544,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574844</v>
+        <v>574913</v>
       </c>
       <c r="R31" t="n">
-        <v>7071940</v>
+        <v>7071700</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3575,11 +3580,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3606,10 +3606,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827146</v>
+        <v>129827141</v>
       </c>
       <c r="B32" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3641,10 +3641,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574908</v>
+        <v>574904</v>
       </c>
       <c r="R32" t="n">
-        <v>7071600</v>
+        <v>7071706</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3703,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827141</v>
+        <v>129827197</v>
       </c>
       <c r="B33" t="n">
-        <v>91641</v>
+        <v>89125</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3714,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3738,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574904</v>
+        <v>574842</v>
       </c>
       <c r="R33" t="n">
-        <v>7071706</v>
+        <v>7071778</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3803,7 +3803,7 @@
         <v>129827164</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
         <v>129827167</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4007,7 +4007,7 @@
         <v>129835984</v>
       </c>
       <c r="B36" t="n">
-        <v>91854</v>
+        <v>91941</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4108,7 +4108,7 @@
         <v>129827196</v>
       </c>
       <c r="B37" t="n">
-        <v>91661</v>
+        <v>91748</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4198,32 +4198,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827171</v>
       </c>
       <c r="B38" t="n">
-        <v>92332</v>
+        <v>57826</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4233,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>574903</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071393</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,6 +4269,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,32 +4300,32 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827204</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>92419</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4335,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574932</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071642</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4392,10 +4397,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827185</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>80285</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4403,21 +4408,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4427,10 +4432,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>574754</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071844</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4463,11 +4468,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4497,7 +4497,7 @@
         <v>129827169</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4599,7 +4599,7 @@
         <v>129827179</v>
       </c>
       <c r="B42" t="n">
-        <v>92094</v>
+        <v>92181</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4693,10 +4693,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827124</v>
+        <v>129827143</v>
       </c>
       <c r="B43" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4728,10 +4728,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575029</v>
+        <v>574888</v>
       </c>
       <c r="R43" t="n">
-        <v>7071789</v>
+        <v>7071636</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4790,10 +4790,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>129827143</v>
+        <v>129827124</v>
       </c>
       <c r="B44" t="n">
-        <v>91641</v>
+        <v>91728</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4825,10 +4825,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>574888</v>
+        <v>575029</v>
       </c>
       <c r="R44" t="n">
-        <v>7071636</v>
+        <v>7071789</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY44"/>
+  <dimension ref="A1:AY43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,45 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129827173</v>
+        <v>129835984</v>
       </c>
       <c r="B2" t="n">
-        <v>57741</v>
+        <v>92123</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>48</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lappticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Amylocystis lapponica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Romell) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
+          <t>Sabbsjöberget, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>574762</v>
+        <v>574908</v>
       </c>
       <c r="R2" t="n">
-        <v>7071667</v>
+        <v>7071708</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,17 +751,13 @@
           <t>2025-11-24</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -777,32 +776,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129827158</v>
+        <v>129827176</v>
       </c>
       <c r="B3" t="n">
-        <v>91641</v>
+        <v>92637</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>67</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Sprickporing</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Diplomitoporus crustulinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Bres.) Domański</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>574924</v>
+        <v>575031</v>
       </c>
       <c r="R3" t="n">
-        <v>7071648</v>
+        <v>7071787</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -854,8 +853,9 @@
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -874,10 +874,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129827151</v>
+        <v>129827197</v>
       </c>
       <c r="B4" t="n">
-        <v>91641</v>
+        <v>89292</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -885,21 +885,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -909,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>574914</v>
+        <v>574842</v>
       </c>
       <c r="R4" t="n">
-        <v>7071623</v>
+        <v>7071778</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -971,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129827135</v>
+        <v>129827199</v>
       </c>
       <c r="B5" t="n">
-        <v>91641</v>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -982,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1006,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>574871</v>
+        <v>574929</v>
       </c>
       <c r="R5" t="n">
-        <v>7071853</v>
+        <v>7071646</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>129827181</v>
       </c>
       <c r="B6" t="n">
-        <v>91939</v>
+        <v>92208</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129827156</v>
+        <v>129827183</v>
       </c>
       <c r="B7" t="n">
-        <v>91641</v>
+        <v>92208</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>574917</v>
+        <v>574913</v>
       </c>
       <c r="R7" t="n">
-        <v>7071640</v>
+        <v>7071700</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129827138</v>
+        <v>129827201</v>
       </c>
       <c r="B8" t="n">
-        <v>91641</v>
+        <v>92605</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>898</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>574868</v>
+        <v>575032</v>
       </c>
       <c r="R8" t="n">
-        <v>7071732</v>
+        <v>7071788</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129827192</v>
+        <v>129827204</v>
       </c>
       <c r="B9" t="n">
-        <v>80200</v>
+        <v>92605</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>898</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blackticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Steccherinum collabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Vesterholt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>574881</v>
+        <v>574932</v>
       </c>
       <c r="R9" t="n">
-        <v>7071589</v>
+        <v>7071642</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129827176</v>
+        <v>129827124</v>
       </c>
       <c r="B10" t="n">
-        <v>92364</v>
+        <v>91909</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>67</v>
+        <v>1202</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sprickporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Diplomitoporus crustulinus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Bres.) Domański</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>575031</v>
+        <v>575029</v>
       </c>
       <c r="R10" t="n">
-        <v>7071787</v>
+        <v>7071789</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1533,9 +1533,8 @@
         <v>0</v>
       </c>
       <c r="AE10" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF10" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1554,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129827131</v>
+        <v>129827126</v>
       </c>
       <c r="B11" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>574994</v>
+        <v>574962</v>
       </c>
       <c r="R11" t="n">
-        <v>7071732</v>
+        <v>7071877</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1651,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129827187</v>
+        <v>129827128</v>
       </c>
       <c r="B12" t="n">
-        <v>80200</v>
+        <v>91909</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1662,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1686,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>575013</v>
+        <v>574950</v>
       </c>
       <c r="R12" t="n">
-        <v>7071709</v>
+        <v>7071890</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1748,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129827190</v>
+        <v>129827130</v>
       </c>
       <c r="B13" t="n">
-        <v>80200</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1759,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1783,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>574872</v>
+        <v>574900</v>
       </c>
       <c r="R13" t="n">
-        <v>7071583</v>
+        <v>7071911</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1845,10 +1844,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129827199</v>
+        <v>129827131</v>
       </c>
       <c r="B14" t="n">
-        <v>89038</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1856,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>510</v>
+        <v>1202</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1880,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>574929</v>
+        <v>574994</v>
       </c>
       <c r="R14" t="n">
-        <v>7071646</v>
+        <v>7071732</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1942,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129827128</v>
+        <v>129827133</v>
       </c>
       <c r="B15" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1977,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>574950</v>
+        <v>574988</v>
       </c>
       <c r="R15" t="n">
-        <v>7071890</v>
+        <v>7071665</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2039,10 +2038,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129827137</v>
+        <v>129827135</v>
       </c>
       <c r="B16" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2074,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>574860</v>
+        <v>574871</v>
       </c>
       <c r="R16" t="n">
-        <v>7071793</v>
+        <v>7071853</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2136,10 +2135,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129827149</v>
+        <v>129827137</v>
       </c>
       <c r="B17" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2171,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>574910</v>
+        <v>574860</v>
       </c>
       <c r="R17" t="n">
-        <v>7071608</v>
+        <v>7071793</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2233,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129827165</v>
+        <v>129827138</v>
       </c>
       <c r="B18" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2244,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2268,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>575010</v>
+        <v>574868</v>
       </c>
       <c r="R18" t="n">
-        <v>7071669</v>
+        <v>7071732</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2304,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2335,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>129827174</v>
+        <v>129827141</v>
       </c>
       <c r="B19" t="n">
-        <v>57741</v>
+        <v>91909</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2346,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2370,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>574764</v>
+        <v>574904</v>
       </c>
       <c r="R19" t="n">
-        <v>7071692</v>
+        <v>7071706</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2406,11 +2400,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål ca 2,3 m upp</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2437,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>129827160</v>
+        <v>129827143</v>
       </c>
       <c r="B20" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2472,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>574930</v>
+        <v>574888</v>
       </c>
       <c r="R20" t="n">
-        <v>7071643</v>
+        <v>7071636</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2534,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>129827188</v>
+        <v>129827146</v>
       </c>
       <c r="B21" t="n">
-        <v>80200</v>
+        <v>91909</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2545,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2569,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>574912</v>
+        <v>574908</v>
       </c>
       <c r="R21" t="n">
-        <v>7071745</v>
+        <v>7071600</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2631,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>129827194</v>
+        <v>129827149</v>
       </c>
       <c r="B22" t="n">
-        <v>80200</v>
+        <v>91909</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2642,21 +2631,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2666,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>574878</v>
+        <v>574910</v>
       </c>
       <c r="R22" t="n">
-        <v>7071591</v>
+        <v>7071608</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2728,10 +2717,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>129827133</v>
+        <v>129827151</v>
       </c>
       <c r="B23" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2763,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>574988</v>
+        <v>574914</v>
       </c>
       <c r="R23" t="n">
-        <v>7071665</v>
+        <v>7071623</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2825,32 +2814,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>129827201</v>
+        <v>129827153</v>
       </c>
       <c r="B24" t="n">
-        <v>92332</v>
+        <v>91909</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>898</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2860,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>575032</v>
+        <v>574910</v>
       </c>
       <c r="R24" t="n">
-        <v>7071788</v>
+        <v>7071631</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2922,10 +2911,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>129827126</v>
+        <v>129827156</v>
       </c>
       <c r="B25" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2957,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>574962</v>
+        <v>574917</v>
       </c>
       <c r="R25" t="n">
-        <v>7071877</v>
+        <v>7071640</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3019,10 +3008,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>129827130</v>
+        <v>129827158</v>
       </c>
       <c r="B26" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3054,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>574900</v>
+        <v>574924</v>
       </c>
       <c r="R26" t="n">
-        <v>7071911</v>
+        <v>7071648</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3116,10 +3105,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>129827153</v>
+        <v>129827160</v>
       </c>
       <c r="B27" t="n">
-        <v>91641</v>
+        <v>91909</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3151,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>574910</v>
+        <v>574930</v>
       </c>
       <c r="R27" t="n">
-        <v>7071631</v>
+        <v>7071643</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3216,11 +3205,11 @@
         <v>129827178</v>
       </c>
       <c r="B28" t="n">
-        <v>92094</v>
+        <v>92369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3310,10 +3299,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>129827183</v>
+        <v>129827179</v>
       </c>
       <c r="B29" t="n">
-        <v>91939</v>
+        <v>92369</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3321,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>1209</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3345,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>574913</v>
+        <v>574866</v>
       </c>
       <c r="R29" t="n">
-        <v>7071700</v>
+        <v>7071723</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3407,10 +3396,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>129827197</v>
+        <v>129827185</v>
       </c>
       <c r="B30" t="n">
-        <v>89038</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3418,21 +3407,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>510</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3442,10 +3431,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>574842</v>
+        <v>574754</v>
       </c>
       <c r="R30" t="n">
-        <v>7071778</v>
+        <v>7071844</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3504,10 +3493,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>129827162</v>
+        <v>129827187</v>
       </c>
       <c r="B31" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3515,21 +3504,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3539,10 +3528,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>574844</v>
+        <v>575013</v>
       </c>
       <c r="R31" t="n">
-        <v>7071940</v>
+        <v>7071709</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3575,11 +3564,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3606,10 +3590,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>129827146</v>
+        <v>129827188</v>
       </c>
       <c r="B32" t="n">
-        <v>91641</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3617,21 +3601,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3641,10 +3625,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>574908</v>
+        <v>574912</v>
       </c>
       <c r="R32" t="n">
-        <v>7071600</v>
+        <v>7071745</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3703,10 +3687,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>129827141</v>
+        <v>129827190</v>
       </c>
       <c r="B33" t="n">
-        <v>91641</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3714,21 +3698,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3738,10 +3722,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>574904</v>
+        <v>574872</v>
       </c>
       <c r="R33" t="n">
-        <v>7071706</v>
+        <v>7071583</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3800,10 +3784,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>129827164</v>
+        <v>129827192</v>
       </c>
       <c r="B34" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3811,21 +3795,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3835,10 +3819,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>574945</v>
+        <v>574881</v>
       </c>
       <c r="R34" t="n">
-        <v>7071651</v>
+        <v>7071589</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3871,11 +3855,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3902,10 +3881,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>129827167</v>
+        <v>129827194</v>
       </c>
       <c r="B35" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3913,21 +3892,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3937,10 +3916,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>574886</v>
+        <v>574878</v>
       </c>
       <c r="R35" t="n">
-        <v>7071594</v>
+        <v>7071591</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3973,11 +3952,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4004,48 +3978,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>129835984</v>
+        <v>129827162</v>
       </c>
       <c r="B36" t="n">
-        <v>91854</v>
+        <v>57953</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>48</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lappticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Amylocystis lapponica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Romell) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sabbsjöberget, Ång</t>
+          <t>Sabbsjöberget A 49258-2025, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>574908</v>
+        <v>574844</v>
       </c>
       <c r="R36" t="n">
-        <v>7071708</v>
+        <v>7071940</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4080,13 +4051,17 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4105,10 +4080,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>129827196</v>
+        <v>129827164</v>
       </c>
       <c r="B37" t="n">
-        <v>91661</v>
+        <v>57953</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4116,19 +4091,23 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr"/>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4136,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>574833</v>
+        <v>574945</v>
       </c>
       <c r="R37" t="n">
-        <v>7071729</v>
+        <v>7071651</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4172,6 +4151,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4198,32 +4182,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>129827204</v>
+        <v>129827165</v>
       </c>
       <c r="B38" t="n">
-        <v>92332</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>898</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Blackticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Steccherinum collabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.) Vesterholt</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4233,10 +4217,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>574932</v>
+        <v>575010</v>
       </c>
       <c r="R38" t="n">
-        <v>7071642</v>
+        <v>7071669</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4269,6 +4253,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4295,10 +4284,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>129827185</v>
+        <v>129827167</v>
       </c>
       <c r="B39" t="n">
-        <v>80200</v>
+        <v>57953</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4306,21 +4295,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4330,10 +4319,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>574754</v>
+        <v>574886</v>
       </c>
       <c r="R39" t="n">
-        <v>7071844</v>
+        <v>7071594</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4366,6 +4355,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4392,10 +4386,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>129827171</v>
+        <v>129827169</v>
       </c>
       <c r="B40" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4427,10 +4421,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>574903</v>
+        <v>575055</v>
       </c>
       <c r="R40" t="n">
-        <v>7071393</v>
+        <v>7071383</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4467,7 +4461,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4494,10 +4488,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>129827169</v>
+        <v>129827171</v>
       </c>
       <c r="B41" t="n">
-        <v>57741</v>
+        <v>57953</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4529,10 +4523,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>575055</v>
+        <v>574903</v>
       </c>
       <c r="R41" t="n">
-        <v>7071383</v>
+        <v>7071393</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4569,7 +4563,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4596,32 +4590,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>129827179</v>
+        <v>129827173</v>
       </c>
       <c r="B42" t="n">
-        <v>92094</v>
+        <v>57953</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4631,10 +4625,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>574866</v>
+        <v>574762</v>
       </c>
       <c r="R42" t="n">
-        <v>7071723</v>
+        <v>7071667</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4667,6 +4661,11 @@
       <c r="AA42" t="inlineStr">
         <is>
           <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4693,10 +4692,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>129827124</v>
+        <v>129827174</v>
       </c>
       <c r="B43" t="n">
-        <v>91641</v>
+        <v>57953</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4704,21 +4703,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4728,10 +4727,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>575029</v>
+        <v>574764</v>
       </c>
       <c r="R43" t="n">
-        <v>7071789</v>
+        <v>7071692</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4766,6 +4765,11 @@
           <t>2025-11-24</t>
         </is>
       </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Bohål ca 2,3 m upp</t>
+        </is>
+      </c>
       <c r="AD43" t="b">
         <v>0</v>
       </c>
@@ -4787,103 +4791,6 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>129827143</v>
-      </c>
-      <c r="B44" t="n">
-        <v>91641</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E44" t="n">
-        <v>1202</v>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Ullticka</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Phellinidium ferrugineofuscum</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="P44" t="inlineStr">
-        <is>
-          <t>Sabbsjöberget A 49258-2025, Ång</t>
-        </is>
-      </c>
-      <c r="Q44" t="n">
-        <v>574888</v>
-      </c>
-      <c r="R44" t="n">
-        <v>7071636</v>
-      </c>
-      <c r="S44" t="n">
-        <v>10</v>
-      </c>
-      <c r="T44" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U44" t="inlineStr">
-        <is>
-          <t>Strömsund</t>
-        </is>
-      </c>
-      <c r="V44" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W44" t="inlineStr">
-        <is>
-          <t>Fjällsjö</t>
-        </is>
-      </c>
-      <c r="Y44" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AA44" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="AD44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG44" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT44" t="inlineStr"/>
-      <c r="AW44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY44" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49258-2025 artfynd.xlsx
+++ b/artfynd/A 49258-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY43"/>
+  <dimension ref="A1:AZ43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129835984</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827176</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827197</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827199</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827181</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827183</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827201</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827204</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827124</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827126</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827128</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827130</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827131</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827133</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827135</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827137</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827138</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827141</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827143</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827146</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2714,6 +2819,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827149</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2811,6 +2921,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827151</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2908,6 +3023,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827153</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3005,6 +3125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827156</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3102,6 +3227,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827158</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3199,6 +3329,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827160</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3296,6 +3431,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827178</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3393,6 +3533,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827179</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3490,6 +3635,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827185</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3587,6 +3737,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827187</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3684,6 +3839,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827188</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3781,6 +3941,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827190</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3878,6 +4043,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827192</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3975,6 +4145,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827194</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4077,6 +4252,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827162</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4179,6 +4359,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827164</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4281,6 +4466,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827165</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4383,6 +4573,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827167</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4485,6 +4680,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827169</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4587,6 +4787,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827171</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4689,6 +4894,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827173</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4791,8 +5001,57 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129827174</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>